--- a/p6_deployment/data/spain/missing/data_preparation/all/df_integrated_missing.xlsx
+++ b/p6_deployment/data/spain/missing/data_preparation/all/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN219"/>
+  <dimension ref="A1:BN220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41747,6 +41747,162 @@
       <c r="BM219" t="inlineStr"/>
       <c r="BN219" t="inlineStr"/>
     </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>UilvTxne</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>45466.6875</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage front stadium
+  cornella de llobregat </t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F220" t="n">
+        <v>33107</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>44</v>
+      </c>
+      <c r="N220" t="n">
+        <v>56</v>
+      </c>
+      <c r="O220" t="n">
+        <v>12</v>
+      </c>
+      <c r="P220" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>2</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2</v>
+      </c>
+      <c r="S220" t="n">
+        <v>24</v>
+      </c>
+      <c r="T220" t="n">
+        <v>18</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="W220" t="n">
+        <v>148</v>
+      </c>
+      <c r="X220" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>20232024</v>
+      </c>
+      <c r="AA220" t="inlineStr"/>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
+      <c r="AE220" t="inlineStr"/>
+      <c r="AF220" t="inlineStr"/>
+      <c r="AG220" t="inlineStr"/>
+      <c r="AH220" t="inlineStr"/>
+      <c r="AI220" t="inlineStr"/>
+      <c r="AJ220" t="inlineStr"/>
+      <c r="AK220" t="inlineStr"/>
+      <c r="AL220" t="inlineStr"/>
+      <c r="AM220" t="inlineStr"/>
+      <c r="AN220" t="inlineStr"/>
+      <c r="AO220" t="n">
+        <v>29.11111111111111</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>179.1666666666667</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>69.4375</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>1907812.5</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>73</v>
+      </c>
+      <c r="BA220" t="inlineStr"/>
+      <c r="BB220" t="inlineStr"/>
+      <c r="BC220" t="inlineStr"/>
+      <c r="BD220" t="inlineStr"/>
+      <c r="BE220" t="inlineStr"/>
+      <c r="BF220" t="inlineStr"/>
+      <c r="BG220" t="inlineStr"/>
+      <c r="BH220" t="inlineStr"/>
+      <c r="BI220" t="inlineStr"/>
+      <c r="BJ220" t="inlineStr"/>
+      <c r="BK220" t="inlineStr"/>
+      <c r="BL220" t="inlineStr"/>
+      <c r="BM220" t="inlineStr"/>
+      <c r="BN220" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
